--- a/email_marketing_forms/018_stay_connected_with_our_organization--email_marketing_forms.xlsx
+++ b/email_marketing_forms/018_stay_connected_with_our_organization--email_marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'no_email'}</t>
+          <t>no_email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'No email'}</t>
+          <t>No email</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'email_marketing_forms'}</t>
+          <t>email_marketing_forms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'Email Marketing Forms'}</t>
+          <t>Email Marketing Forms</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
